--- a/02-示例报表/密码条清单-示例.xlsx
+++ b/02-示例报表/密码条清单-示例.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="142">
   <si>
     <t>密码条</t>
   </si>
@@ -34,7 +34,7 @@
     <t>个人赛</t>
   </si>
   <si>
-    <t>8H7G-YH6C</t>
+    <t>2MYU-CXND</t>
   </si>
   <si>
     <t>专业评审</t>
@@ -52,7 +52,7 @@
     <t>未投</t>
   </si>
   <si>
-    <t>U7CC-GYGU</t>
+    <t>5XPV-4BS6</t>
   </si>
   <si>
     <t>专业评审2</t>
@@ -61,7 +61,7 @@
     <t>评审2</t>
   </si>
   <si>
-    <t>JAX7-G2BF</t>
+    <t>W8FN-SR7E</t>
   </si>
   <si>
     <t>专业评审3</t>
@@ -70,16 +70,7 @@
     <t>评审3</t>
   </si>
   <si>
-    <t>WL74-DSF4</t>
-  </si>
-  <si>
-    <t>专业评审4</t>
-  </si>
-  <si>
-    <t>评审4</t>
-  </si>
-  <si>
-    <t>2TDS-2572</t>
+    <t>KWRW-EYZM</t>
   </si>
   <si>
     <t>大众评审</t>
@@ -94,355 +85,355 @@
     <t>已投</t>
   </si>
   <si>
-    <t>9MSG-47MX</t>
+    <t>9A9G-LPXD</t>
   </si>
   <si>
     <t>大众评审02</t>
   </si>
   <si>
-    <t>NRXU-8D8W</t>
+    <t>VKHH-U35S</t>
   </si>
   <si>
     <t>大众评审03</t>
   </si>
   <si>
-    <t>KCYP-3RAK</t>
+    <t>6S2S-H6N4</t>
   </si>
   <si>
     <t>大众评审04</t>
   </si>
   <si>
-    <t>KV3K-CQDN</t>
+    <t>96HE-4S2Y</t>
   </si>
   <si>
     <t>大众评审05</t>
   </si>
   <si>
-    <t>L6GT-NX84</t>
+    <t>5V6Z-4NY2</t>
   </si>
   <si>
     <t>大众评审06</t>
   </si>
   <si>
-    <t>YKKQ-KGEZ</t>
+    <t>XC2T-8Z6H</t>
   </si>
   <si>
     <t>大众评审07</t>
   </si>
   <si>
-    <t>JWXY-X6RP</t>
+    <t>5R3Z-2UDU</t>
   </si>
   <si>
     <t>大众评审08</t>
   </si>
   <si>
-    <t>DW9K-DD8Y</t>
+    <t>WUYZ-JXGD</t>
   </si>
   <si>
     <t>大众评审09</t>
   </si>
   <si>
-    <t>C676-68BZ</t>
+    <t>MFUR-7HBR</t>
   </si>
   <si>
     <t>大众评审10</t>
   </si>
   <si>
-    <t>C84G-3QDW</t>
+    <t>PQMZ-VZ39</t>
   </si>
   <si>
     <t>大众评审11</t>
   </si>
   <si>
-    <t>2Y3W-2VM5</t>
+    <t>LC83-U2G7</t>
   </si>
   <si>
     <t>大众评审12</t>
   </si>
   <si>
-    <t>DMRN-NSQU</t>
+    <t>W54M-7F64</t>
   </si>
   <si>
     <t>大众评审13</t>
   </si>
   <si>
-    <t>LLK4-LJQU</t>
+    <t>UXJV-E4PA</t>
   </si>
   <si>
     <t>大众评审14</t>
   </si>
   <si>
-    <t>2J8P-WF5G</t>
+    <t>E7FY-VD9B</t>
   </si>
   <si>
     <t>大众评审15</t>
   </si>
   <si>
-    <t>JQUR-4G8W</t>
+    <t>7TCK-HFV4</t>
   </si>
   <si>
     <t>大众评审16</t>
   </si>
   <si>
-    <t>KCWG-U47C</t>
+    <t>REY3-MZBD</t>
   </si>
   <si>
     <t>大众评审17</t>
   </si>
   <si>
-    <t>UBH5-J36T</t>
+    <t>XKZ4-B77M</t>
   </si>
   <si>
     <t>大众评审18</t>
   </si>
   <si>
-    <t>G7UA-BLEC</t>
+    <t>R3NM-M9RH</t>
   </si>
   <si>
     <t>大众评审19</t>
   </si>
   <si>
-    <t>FCME-CJUT</t>
+    <t>6B38-C36H</t>
   </si>
   <si>
     <t>大众评审20</t>
   </si>
   <si>
-    <t>73CM-LKSS</t>
+    <t>U967-TLVZ</t>
   </si>
   <si>
     <t>大众评审21</t>
   </si>
   <si>
-    <t>9N58-M5HS</t>
+    <t>KT3E-GWKZ</t>
   </si>
   <si>
     <t>大众评审22</t>
   </si>
   <si>
-    <t>X4KJ-R6GY</t>
+    <t>DW63-3T9H</t>
   </si>
   <si>
     <t>大众评审23</t>
   </si>
   <si>
-    <t>DCUK-GW9M</t>
+    <t>WL58-2GLH</t>
   </si>
   <si>
     <t>大众评审24</t>
   </si>
   <si>
-    <t>96RL-L7BC</t>
+    <t>Y5GC-QM84</t>
   </si>
   <si>
     <t>大众评审25</t>
   </si>
   <si>
-    <t>HD3N-4MET</t>
+    <t>FU5U-WA4X</t>
   </si>
   <si>
     <t>大众评审26</t>
   </si>
   <si>
-    <t>4CP4-W9DW</t>
+    <t>CQXH-6AUB</t>
   </si>
   <si>
     <t>大众评审27</t>
   </si>
   <si>
-    <t>ZMF6-MC5Q</t>
+    <t>CRK6-5E5A</t>
   </si>
   <si>
     <t>大众评审28</t>
   </si>
   <si>
-    <t>VCRW-Q66V</t>
+    <t>XS59-JD2U</t>
   </si>
   <si>
     <t>大众评审29</t>
   </si>
   <si>
-    <t>RZ4R-3WQA</t>
+    <t>YBCM-PF5D</t>
   </si>
   <si>
     <t>大众评审30</t>
   </si>
   <si>
-    <t>Z98A-XAKE</t>
+    <t>7NY2-6QR6</t>
   </si>
   <si>
     <t>大众评审31</t>
   </si>
   <si>
-    <t>EZ7H-9W87</t>
+    <t>2S3T-RHLU</t>
   </si>
   <si>
     <t>大众评审32</t>
   </si>
   <si>
-    <t>ZPMU-GA29</t>
+    <t>N9X9-C5YQ</t>
   </si>
   <si>
     <t>大众评审33</t>
   </si>
   <si>
-    <t>6V9Z-4G7L</t>
+    <t>PFCJ-VFTU</t>
   </si>
   <si>
     <t>大众评审34</t>
   </si>
   <si>
-    <t>DZEL-ZVXX</t>
+    <t>XG5R-E7JV</t>
   </si>
   <si>
     <t>大众评审35</t>
   </si>
   <si>
-    <t>TZPD-QZE2</t>
+    <t>KZZR-5P4A</t>
   </si>
   <si>
     <t>大众评审36</t>
   </si>
   <si>
-    <t>Y7CL-6PUF</t>
+    <t>QHEF-2XWN</t>
   </si>
   <si>
     <t>大众评审37</t>
   </si>
   <si>
-    <t>DJAP-JBWS</t>
+    <t>BSWP-L5NZ</t>
   </si>
   <si>
     <t>大众评审38</t>
   </si>
   <si>
-    <t>4VET-GBXM</t>
+    <t>FVSB-2TPY</t>
   </si>
   <si>
     <t>大众评审39</t>
   </si>
   <si>
-    <t>Z3GD-YFRT</t>
+    <t>8V7Q-99BG</t>
   </si>
   <si>
     <t>大众评审40</t>
   </si>
   <si>
-    <t>3G32-CLZC</t>
+    <t>EDKR-D5HH</t>
   </si>
   <si>
     <t>大众评审41</t>
   </si>
   <si>
-    <t>QDBZ-XH77</t>
+    <t>TN2K-CKCJ</t>
   </si>
   <si>
     <t>大众评审42</t>
   </si>
   <si>
-    <t>ML3B-TR9T</t>
+    <t>WLFM-XRDA</t>
   </si>
   <si>
     <t>大众评审43</t>
   </si>
   <si>
-    <t>F88B-CB3Q</t>
+    <t>8QWM-HLJE</t>
   </si>
   <si>
     <t>大众评审44</t>
   </si>
   <si>
-    <t>JBVC-QQYA</t>
+    <t>LXVM-9ZK7</t>
   </si>
   <si>
     <t>大众评审45</t>
   </si>
   <si>
-    <t>A4HD-NGWE</t>
+    <t>C4K3-3QXT</t>
   </si>
   <si>
     <t>大众评审46</t>
   </si>
   <si>
-    <t>8TBM-5PUL</t>
+    <t>2WDT-GZPF</t>
   </si>
   <si>
     <t>大众评审47</t>
   </si>
   <si>
-    <t>SGLH-D8TD</t>
+    <t>GFWY-J4N2</t>
   </si>
   <si>
     <t>大众评审48</t>
   </si>
   <si>
-    <t>FPNQ-CW3Z</t>
+    <t>GWFH-SHFX</t>
   </si>
   <si>
     <t>大众评审49</t>
   </si>
   <si>
-    <t>5EBZ-XM44</t>
+    <t>T9W9-KDVS</t>
   </si>
   <si>
     <t>大众评审50</t>
   </si>
   <si>
-    <t>5TQW-SLDJ</t>
+    <t>SFA5-2W3X</t>
   </si>
   <si>
     <t>大众评审51</t>
   </si>
   <si>
-    <t>HZ3K-YEZ8</t>
+    <t>S2K5-JQNQ</t>
   </si>
   <si>
     <t>大众评审52</t>
   </si>
   <si>
-    <t>MCSX-H63F</t>
+    <t>L2TP-PBMX</t>
   </si>
   <si>
     <t>大众评审53</t>
   </si>
   <si>
-    <t>PPRS-J48Z</t>
+    <t>SWZD-53WD</t>
   </si>
   <si>
     <t>大众评审54</t>
   </si>
   <si>
-    <t>XLA5-Y9XJ</t>
+    <t>4QRL-ENWM</t>
   </si>
   <si>
     <t>大众评审55</t>
   </si>
   <si>
-    <t>ZCJT-P2GJ</t>
+    <t>J9RS-B8CN</t>
   </si>
   <si>
     <t>大众评审56</t>
   </si>
   <si>
-    <t>ANSH-UW9W</t>
+    <t>8DZL-UJHP</t>
   </si>
   <si>
     <t>大众评审57</t>
   </si>
   <si>
-    <t>ANMV-TT9P</t>
+    <t>AUDZ-R8ZR</t>
   </si>
   <si>
     <t>大众评审58</t>
   </si>
   <si>
-    <t>2QBT-NYPV</t>
+    <t>FAHZ-K5TC</t>
   </si>
   <si>
     <t>大众评审59</t>
   </si>
   <si>
-    <t>6D48-E4HC</t>
+    <t>JEDP-AGP9</t>
   </si>
   <si>
     <t>大众评审60</t>
@@ -841,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -947,19 +938,19 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -967,252 +958,252 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
@@ -1220,85 +1211,85 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -1307,113 +1298,113 @@
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
         <v>55</v>
       </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
         <v>59</v>
       </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
         <v>63</v>
       </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
@@ -1427,39 +1418,39 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
         <v>67</v>
       </c>
-      <c r="B27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -1468,142 +1459,142 @@
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
         <v>71</v>
       </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" t="s">
-        <v>72</v>
-      </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
         <v>75</v>
       </c>
-      <c r="B31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" t="s">
-        <v>76</v>
-      </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
         <v>79</v>
       </c>
-      <c r="B33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -1611,85 +1602,85 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
         <v>83</v>
       </c>
-      <c r="B35" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" t="s">
-        <v>84</v>
-      </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
         <v>87</v>
       </c>
-      <c r="B37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
       <c r="D37" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
         <v>11</v>
@@ -1698,27 +1689,27 @@
         <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>12</v>
@@ -1726,114 +1717,114 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" t="s">
         <v>91</v>
       </c>
-      <c r="B39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
-      </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
         <v>95</v>
       </c>
-      <c r="B41" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" t="s">
-        <v>96</v>
-      </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
         <v>99</v>
       </c>
-      <c r="B43" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" t="s">
-        <v>100</v>
-      </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -1841,16 +1832,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>11</v>
@@ -1859,211 +1850,211 @@
         <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" t="s">
         <v>103</v>
       </c>
-      <c r="B45" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" t="s">
-        <v>104</v>
-      </c>
       <c r="D45" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" t="s">
         <v>107</v>
       </c>
-      <c r="B47" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" t="s">
-        <v>108</v>
-      </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="D48" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" t="s">
         <v>111</v>
       </c>
-      <c r="B49" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" t="s">
-        <v>112</v>
-      </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" t="s">
         <v>115</v>
       </c>
-      <c r="B51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" t="s">
-        <v>116</v>
-      </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E51" t="s">
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" t="s">
         <v>119</v>
       </c>
-      <c r="B53" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" t="s">
-        <v>120</v>
-      </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -2071,39 +2062,39 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" t="s">
         <v>123</v>
       </c>
-      <c r="B55" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" t="s">
-        <v>124</v>
-      </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E55" t="s">
         <v>11</v>
@@ -2112,142 +2103,142 @@
         <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="D56" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
         <v>127</v>
       </c>
-      <c r="B57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" t="s">
-        <v>128</v>
-      </c>
       <c r="D57" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
       </c>
       <c r="F57" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" t="s">
         <v>131</v>
       </c>
-      <c r="B59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" t="s">
-        <v>132</v>
-      </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E59" t="s">
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" t="s">
         <v>135</v>
       </c>
-      <c r="B61" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" t="s">
-        <v>136</v>
-      </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E61" t="s">
         <v>11</v>
       </c>
       <c r="F61" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G61" t="s">
         <v>12</v>
@@ -2255,94 +2246,71 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" t="s">
         <v>139</v>
       </c>
-      <c r="B63" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" t="s">
-        <v>140</v>
-      </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="F63" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D64" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>143</v>
-      </c>
-      <c r="B65" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" t="s">
-        <v>144</v>
-      </c>
-      <c r="D65" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
